--- a/04_DESIGN_TABLES/DesignTable_2613.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2613.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,6 +514,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -800,6 +805,88 @@
       <c r="R6" t="inlineStr">
         <is>
           <t>DROP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2613-04-04-04-FG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2613-04-04-04-FG</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1/4-18 (A (1) NPTF) x 1/4-18 (A (2) NPTF) x 7/16-20 (B UN/UNF-2A)</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / flats / bores from the Brennan TFA catalog p.53; tap drill = Air-Way per size (A1); thread majors from the end library</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.53 alone; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2613-04-04-04-FG</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_2613.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2613.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.53 alone; marked DimSource BRENNAN</t>
+          <t>2026-10-20 (batch 19 staging, tools/_out/batch19_20261021/B_newspec, NOT shipped): values checked against Brennan TFA p.53 TFA-p053-t02 (L 1.090 = N5, L1 0.880 = N1, M 1.220 = M1, Y FLATS 0.750 = Y1, A1 DRILL 0.281 = D1, B3 DRILL 0.172 = D) - all equal; gate TOOLCHAIN cleared - gen_tee SPEC 2613 (forged tee, legs NPTFM / NPTFF / JICM); DataStatus MISSING -&gt; ASSUMED. NOTE for the user: Air-Way s181 prints the PLAIN 2613-04-04-04 (not the forged -FG): N5 1.09 / N1 0.88 / Y1 0.75 / D1 0.28 / D 0.17 / TAPDRILL 0.43 agree, M1 1.01 vs Brennan forged 1.22 - built to the Brennan -FG value (the plain part is another part; Air-Way has no -FG row) | was: 2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.53 alone; marked DimSource BRENNAN</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
